--- a/testAffichageML/ig/StructureDefinition-fr-cda-section-antecedents-familiaux.xlsx
+++ b/testAffichageML/ig/StructureDefinition-fr-cda-section-antecedents-familiaux.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T09:34:46+00:00</t>
+    <t>2026-05-18T13:21:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
